--- a/esyluban/examples/dev/DataTables/test/table_one.xlsx
+++ b/esyluban/examples/dev/DataTables/test/table_one.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.375" customWidth="1" min="3" max="3"/>
@@ -425,7 +425,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="test.TbSingleton" &amp; value_type="test.DemoSingletonType" &amp; mode="one" &amp; read_schema_from_file="false" &amp; input="test/table_one.xlsx" &amp; output="test_tbsingleton"</t>
+          <t>full_name="test.TbSingleton" &amp; value_type="test.DemoSingletonType" &amp; mode="one" &amp; input="test/table_one.xlsx"</t>
         </is>
       </c>
     </row>
@@ -503,52 +503,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>

--- a/esyluban/examples/dev/DataTables/test/table_one.xlsx
+++ b/esyluban/examples/dev/DataTables/test/table_one.xlsx
@@ -505,8 +505,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
